--- a/acronym-quiz/records/Quiz Scores.xlsx
+++ b/acronym-quiz/records/Quiz Scores.xlsx
@@ -79,7 +79,19 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosita Visitacion</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29 / 30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:B3"/>
 </worksheet>
 </file>